--- a/Techniques/AI Driven Machine Learning and Clustering/items_mhi_ansaldo.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/items_mhi_ansaldo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data driven predictive maintenance\AI Driven Machine Learning and Clustering\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data driven predictive maintenance\Techniques\AI Driven Machine Learning and Clustering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6F4FD7-986E-4D4D-AC85-28A0B8151FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCBC1C5-A391-489F-99FD-0ECCC9782469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
